--- a/static/data/Extended-Indexes.xlsx
+++ b/static/data/Extended-Indexes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ444"/>
+  <dimension ref="A1:AQ445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51616,6 +51616,139 @@
         <v>4.5</v>
       </c>
     </row>
+    <row r="445">
+      <c r="A445" s="1" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B445" t="n">
+        <v>0</v>
+      </c>
+      <c r="C445" t="n">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="D445" t="n">
+        <v>44.82758620689656</v>
+      </c>
+      <c r="E445" t="n">
+        <v>76.92307692307693</v>
+      </c>
+      <c r="F445" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="G445" t="n">
+        <v>45870.83333333334</v>
+      </c>
+      <c r="H445" t="n">
+        <v>0.9523809523809524</v>
+      </c>
+      <c r="I445" t="n">
+        <v>-0.1052631578947369</v>
+      </c>
+      <c r="J445" t="n">
+        <v>0.7954545454545454</v>
+      </c>
+      <c r="K445" t="n">
+        <v>1.052631578947368</v>
+      </c>
+      <c r="L445" t="n">
+        <v>1.825</v>
+      </c>
+      <c r="M445" t="n">
+        <v>2.175</v>
+      </c>
+      <c r="N445" t="n">
+        <v>3.708333333333333</v>
+      </c>
+      <c r="O445" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P445" t="n">
+        <v>72.88</v>
+      </c>
+      <c r="Q445" t="n">
+        <v>34.78947368421053</v>
+      </c>
+      <c r="R445" t="n">
+        <v>-0.04375000000000009</v>
+      </c>
+      <c r="S445" t="n">
+        <v>-0.8647058823529412</v>
+      </c>
+      <c r="T445" t="n">
+        <v>0.8058823529411767</v>
+      </c>
+      <c r="U445" t="n">
+        <v>1.352941176470588</v>
+      </c>
+      <c r="V445" t="n">
+        <v>45.99999999999999</v>
+      </c>
+      <c r="W445" t="n">
+        <v>58.62068965517241</v>
+      </c>
+      <c r="X445" t="n">
+        <v>54.16666666666666</v>
+      </c>
+      <c r="Y445" t="n">
+        <v>39.28571428571428</v>
+      </c>
+      <c r="Z445" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA445" t="n">
+        <v>68.96551724137932</v>
+      </c>
+      <c r="AB445" t="n">
+        <v>76</v>
+      </c>
+      <c r="AC445" t="n">
+        <v>68.96551724137932</v>
+      </c>
+      <c r="AD445" t="n">
+        <v>41.66666666666667</v>
+      </c>
+      <c r="AE445" t="n">
+        <v>22.125</v>
+      </c>
+      <c r="AF445" t="n">
+        <v>30.04</v>
+      </c>
+      <c r="AG445" t="n">
+        <v>48.27586206896552</v>
+      </c>
+      <c r="AH445" t="n">
+        <v>52</v>
+      </c>
+      <c r="AI445" t="n">
+        <v>75.86206896551724</v>
+      </c>
+      <c r="AJ445" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK445" t="n">
+        <v>58.62068965517241</v>
+      </c>
+      <c r="AL445" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM445" t="n">
+        <v>6.583333333333334</v>
+      </c>
+      <c r="AN445" t="n">
+        <v>8.925925925925926</v>
+      </c>
+      <c r="AO445" t="n">
+        <v>6.65263157894737</v>
+      </c>
+      <c r="AP445" t="n">
+        <v>7.175925925925927</v>
+      </c>
+      <c r="AQ445" t="n">
+        <v>5.828947368421054</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/static/data/Extended-Indexes.xlsx
+++ b/static/data/Extended-Indexes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ445"/>
+  <dimension ref="A1:AQ446"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51496,124 +51496,124 @@
         <v>5.88235294117647</v>
       </c>
       <c r="D444" t="n">
-        <v>63.63636363636363</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="E444" t="n">
         <v>58.82352941176471</v>
       </c>
       <c r="F444" t="n">
-        <v>10</v>
+        <v>9.090909090909092</v>
       </c>
       <c r="G444" t="n">
-        <v>46500</v>
+        <v>46791.66666666666</v>
       </c>
       <c r="H444" t="n">
-        <v>-1.75</v>
+        <v>-1.544444444444445</v>
       </c>
       <c r="I444" t="n">
         <v>-1.291176470588235</v>
       </c>
       <c r="J444" t="n">
-        <v>-1.5</v>
+        <v>-1.3</v>
       </c>
       <c r="K444" t="n">
         <v>0.1176470588235294</v>
       </c>
       <c r="L444" t="n">
-        <v>-2.120217581749431e-16</v>
+        <v>0.09999999999999983</v>
       </c>
       <c r="M444" t="n">
         <v>1.647058823529412</v>
       </c>
       <c r="N444" t="n">
-        <v>4.300000000000001</v>
+        <v>4.454545454545455</v>
       </c>
       <c r="O444" t="n">
         <v>2.5</v>
       </c>
       <c r="P444" t="n">
-        <v>40.1111111111111</v>
+        <v>46.09999999999999</v>
       </c>
       <c r="Q444" t="n">
         <v>25.67647058823529</v>
       </c>
       <c r="R444" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="S444" t="n">
-        <v>-2</v>
+        <v>-1.366666666666667</v>
       </c>
       <c r="T444" t="n">
-        <v>2.333333333333333</v>
+        <v>1.75</v>
       </c>
       <c r="U444" t="n">
-        <v>2.6</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="V444" t="n">
-        <v>6.25</v>
+        <v>15</v>
       </c>
       <c r="W444" t="n">
-        <v>54.54545454545454</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="X444" t="n">
         <v>41.17647058823529</v>
       </c>
       <c r="Y444" t="n">
-        <v>27.27272727272727</v>
+        <v>25</v>
       </c>
       <c r="Z444" t="n">
         <v>41.17647058823529</v>
       </c>
       <c r="AA444" t="n">
-        <v>54.54545454545454</v>
+        <v>50</v>
       </c>
       <c r="AB444" t="n">
         <v>58.82352941176471</v>
       </c>
       <c r="AC444" t="n">
-        <v>81.81818181818183</v>
+        <v>75</v>
       </c>
       <c r="AD444" t="n">
         <v>81.25</v>
       </c>
       <c r="AE444" t="n">
-        <v>11.45454545454546</v>
+        <v>11.33333333333334</v>
       </c>
       <c r="AF444" t="n">
         <v>16</v>
       </c>
       <c r="AG444" t="n">
-        <v>63.63636363636363</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="AH444" t="n">
         <v>52.94117647058824</v>
       </c>
       <c r="AI444" t="n">
-        <v>72.72727272727273</v>
+        <v>75</v>
       </c>
       <c r="AJ444" t="n">
         <v>76.47058823529412</v>
       </c>
       <c r="AK444" t="n">
-        <v>63.63636363636363</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="AL444" t="n">
         <v>29.41176470588236</v>
       </c>
       <c r="AM444" t="n">
-        <v>3.10909090909091</v>
+        <v>3.100000000000001</v>
       </c>
       <c r="AN444" t="n">
-        <v>6.681818181818182</v>
+        <v>6.375</v>
       </c>
       <c r="AO444" t="n">
-        <v>7.1</v>
+        <v>6.416666666666666</v>
       </c>
       <c r="AP444" t="n">
-        <v>6.000000000000001</v>
+        <v>5.75</v>
       </c>
       <c r="AQ444" t="n">
-        <v>4.5</v>
+        <v>4.199999999999999</v>
       </c>
     </row>
     <row r="445">
@@ -51626,13 +51626,13 @@
         <v>0</v>
       </c>
       <c r="C445" t="n">
-        <v>7.692307692307693</v>
+        <v>6.896551724137931</v>
       </c>
       <c r="D445" t="n">
         <v>44.82758620689656</v>
       </c>
       <c r="E445" t="n">
-        <v>76.92307692307693</v>
+        <v>75.86206896551724</v>
       </c>
       <c r="F445" t="n">
         <v>14.28571428571428</v>
@@ -51644,31 +51644,31 @@
         <v>0.9523809523809524</v>
       </c>
       <c r="I445" t="n">
-        <v>-0.1052631578947369</v>
+        <v>-0.09523809523809519</v>
       </c>
       <c r="J445" t="n">
         <v>0.7954545454545454</v>
       </c>
       <c r="K445" t="n">
-        <v>1.052631578947368</v>
+        <v>0.9523809523809527</v>
       </c>
       <c r="L445" t="n">
         <v>1.825</v>
       </c>
       <c r="M445" t="n">
-        <v>2.175</v>
+        <v>2.522727272727273</v>
       </c>
       <c r="N445" t="n">
         <v>3.708333333333333</v>
       </c>
       <c r="O445" t="n">
-        <v>2.5</v>
+        <v>2.954545454545455</v>
       </c>
       <c r="P445" t="n">
         <v>72.88</v>
       </c>
       <c r="Q445" t="n">
-        <v>34.78947368421053</v>
+        <v>34.09523809523809</v>
       </c>
       <c r="R445" t="n">
         <v>-0.04375000000000009</v>
@@ -51689,49 +51689,49 @@
         <v>58.62068965517241</v>
       </c>
       <c r="X445" t="n">
-        <v>54.16666666666666</v>
+        <v>51.85185185185185</v>
       </c>
       <c r="Y445" t="n">
         <v>39.28571428571428</v>
       </c>
       <c r="Z445" t="n">
-        <v>28</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="AA445" t="n">
         <v>68.96551724137932</v>
       </c>
       <c r="AB445" t="n">
-        <v>76</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="AC445" t="n">
         <v>68.96551724137932</v>
       </c>
       <c r="AD445" t="n">
-        <v>41.66666666666667</v>
+        <v>42.30769230769231</v>
       </c>
       <c r="AE445" t="n">
         <v>22.125</v>
       </c>
       <c r="AF445" t="n">
-        <v>30.04</v>
+        <v>29.67857142857143</v>
       </c>
       <c r="AG445" t="n">
         <v>48.27586206896552</v>
       </c>
       <c r="AH445" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="AI445" t="n">
         <v>75.86206896551724</v>
       </c>
       <c r="AJ445" t="n">
-        <v>75</v>
+        <v>74.07407407407408</v>
       </c>
       <c r="AK445" t="n">
         <v>58.62068965517241</v>
       </c>
       <c r="AL445" t="n">
-        <v>32</v>
+        <v>32.14285714285715</v>
       </c>
       <c r="AM445" t="n">
         <v>6.583333333333334</v>
@@ -51747,6 +51747,137 @@
       </c>
       <c r="AQ445" t="n">
         <v>5.828947368421054</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="1" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B446" t="n">
+        <v>0</v>
+      </c>
+      <c r="C446" t="n">
+        <v>4.347826086956522</v>
+      </c>
+      <c r="D446" t="n">
+        <v>44.44444444444444</v>
+      </c>
+      <c r="E446" t="n">
+        <v>39.1304347826087</v>
+      </c>
+      <c r="F446" t="n">
+        <v>0</v>
+      </c>
+      <c r="G446" t="n">
+        <v>37360</v>
+      </c>
+      <c r="H446" t="n">
+        <v>-0.5000000000000001</v>
+      </c>
+      <c r="I446" t="n">
+        <v>0.5029411764705882</v>
+      </c>
+      <c r="J446" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="K446" t="n">
+        <v>0.5833333333333333</v>
+      </c>
+      <c r="L446" t="n">
+        <v>2.166666666666667</v>
+      </c>
+      <c r="M446" t="n">
+        <v>1.315789473684211</v>
+      </c>
+      <c r="N446" t="n">
+        <v>9.428571428571429</v>
+      </c>
+      <c r="O446" t="n">
+        <v>5.222222222222222</v>
+      </c>
+      <c r="P446" t="n">
+        <v>59.83333333333334</v>
+      </c>
+      <c r="Q446" t="n">
+        <v>43.23529411764706</v>
+      </c>
+      <c r="R446" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="S446" t="n">
+        <v>0</v>
+      </c>
+      <c r="T446" t="n">
+        <v>1</v>
+      </c>
+      <c r="U446" t="n">
+        <v>2</v>
+      </c>
+      <c r="V446" t="inlineStr"/>
+      <c r="W446" t="n">
+        <v>55.55555555555556</v>
+      </c>
+      <c r="X446" t="n">
+        <v>40.90909090909091</v>
+      </c>
+      <c r="Y446" t="n">
+        <v>22.22222222222222</v>
+      </c>
+      <c r="Z446" t="n">
+        <v>27.27272727272727</v>
+      </c>
+      <c r="AA446" t="n">
+        <v>55.55555555555556</v>
+      </c>
+      <c r="AB446" t="n">
+        <v>69.56521739130434</v>
+      </c>
+      <c r="AC446" t="n">
+        <v>44.44444444444444</v>
+      </c>
+      <c r="AD446" t="n">
+        <v>65.21739130434783</v>
+      </c>
+      <c r="AE446" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF446" t="n">
+        <v>18.77272727272728</v>
+      </c>
+      <c r="AG446" t="n">
+        <v>44.44444444444444</v>
+      </c>
+      <c r="AH446" t="n">
+        <v>54.54545454545454</v>
+      </c>
+      <c r="AI446" t="n">
+        <v>77.77777777777779</v>
+      </c>
+      <c r="AJ446" t="n">
+        <v>42.85714285714285</v>
+      </c>
+      <c r="AK446" t="n">
+        <v>55.55555555555556</v>
+      </c>
+      <c r="AL446" t="n">
+        <v>27.27272727272727</v>
+      </c>
+      <c r="AM446" t="n">
+        <v>3.266666666666666</v>
+      </c>
+      <c r="AN446" t="n">
+        <v>7.055555555555555</v>
+      </c>
+      <c r="AO446" t="n">
+        <v>4.833333333333334</v>
+      </c>
+      <c r="AP446" t="n">
+        <v>7.277777777777778</v>
+      </c>
+      <c r="AQ446" t="n">
+        <v>5.166666666666667</v>
       </c>
     </row>
   </sheetData>

--- a/static/data/Extended-Indexes.xlsx
+++ b/static/data/Extended-Indexes.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,228 +413,228 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ446"/>
+  <dimension ref="A1:AQ447"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>US Stock Valuation Sentiment -- Institutional</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>US Stock Valuation Sentiment -- Individual</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>US Stock Trend Cause -- Institutional</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>US Stock Trend Cause -- Individual</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Japan Stock Valuation Sentiment -- Institutional</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Dow Fundamental Valuation Level -- Institutional</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Dow Expected Change (1M) -- Institutional</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Dow Expected Change (1M) -- Individual</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Dow Expected Change (3M) -- Institutional</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Dow Expected Change (3M) -- Individual</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Dow Expected Change (6M) -- Institutional</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Dow Expected Change (6M) -- Individual</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Dow Expected Change (1Y) -- Institutional</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Dow Expected Change (1Y) -- Individual</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Dow Expected Change (10Y) -- Institutional</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Dow Expected Change (10Y) -- Individual</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Nikkei Expected Change (1M) -- Institutional</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Nikkei Expected Change (3M) -- Institutional</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Nikkei Expected Change (6M) -- Institutional</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Nikkei Expected Change (1Y) -- Institutional</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Nikkei Expected Change (10Y) -- Institutional</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Market Timing Advice (Peak) -- Institutional</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Market Timing Advice (Peak) -- Individual</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Market Timing Advice (Trough) -- Institutional</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Market Timing Advice (Trough) -- Individual</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Optimism Influence -- Institutional</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Optimism Influence -- Individual</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Pessimism Influence -- Institutional</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Pessimism Influence -- Individual</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Crash Probability (6M) -- Institutional</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Crash Probability (6M) -- Individual</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Post-Drop 3% Reaction -- Institutional</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Post-Drop 3% Reaction -- Individual</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Post-Drop 25% Reaction -- Institutional</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Post-Drop 25% Reaction -- Individual</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Current Investment Inclination -- Institutional</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Current Investment Inclination -- Individual</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>Inflation Expectation (10Y) -- Institutional</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>Corporate Earnings Growth (US, 3Y) -- Institutional</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>Corporate Earnings Growth (Japan, 3Y) -- Institutional</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>Corporate Earnings Growth (US, 10Y) -- Institutional</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>Corporate Earnings Growth (Japan, 10Y) -- Institutional</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>1989-06</t>
         </is>
@@ -727,7 +715,7 @@
       <c r="AQ2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>1989-07</t>
         </is>
@@ -828,7 +816,7 @@
       <c r="AQ3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>1989-08</t>
         </is>
@@ -929,7 +917,7 @@
       <c r="AQ4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>1989-09</t>
         </is>
@@ -978,7 +966,7 @@
       <c r="AQ5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>1989-10</t>
         </is>
@@ -1027,7 +1015,7 @@
       <c r="AQ6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>1989-11</t>
         </is>
@@ -1076,7 +1064,7 @@
       <c r="AQ7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>1989-12</t>
         </is>
@@ -1125,7 +1113,7 @@
       <c r="AQ8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>1990-01</t>
         </is>
@@ -1210,7 +1198,7 @@
       <c r="AQ9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>1990-02</t>
         </is>
@@ -1295,7 +1283,7 @@
       <c r="AQ10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>1990-03</t>
         </is>
@@ -1380,7 +1368,7 @@
       <c r="AQ11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>1990-04</t>
         </is>
@@ -1429,7 +1417,7 @@
       <c r="AQ12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>1990-05</t>
         </is>
@@ -1478,7 +1466,7 @@
       <c r="AQ13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>1990-06</t>
         </is>
@@ -1527,7 +1515,7 @@
       <c r="AQ14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>1990-07</t>
         </is>
@@ -1612,7 +1600,7 @@
       <c r="AQ15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>1990-08</t>
         </is>
@@ -1697,7 +1685,7 @@
       <c r="AQ16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>1990-09</t>
         </is>
@@ -1782,7 +1770,7 @@
       <c r="AQ17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>1990-10</t>
         </is>
@@ -1831,7 +1819,7 @@
       <c r="AQ18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>1990-11</t>
         </is>
@@ -1880,7 +1868,7 @@
       <c r="AQ19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>1990-12</t>
         </is>
@@ -1929,7 +1917,7 @@
       <c r="AQ20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>1991-01</t>
         </is>
@@ -2014,7 +2002,7 @@
       <c r="AQ21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>1991-02</t>
         </is>
@@ -2099,7 +2087,7 @@
       <c r="AQ22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>1991-03</t>
         </is>
@@ -2184,7 +2172,7 @@
       <c r="AQ23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>1991-04</t>
         </is>
@@ -2261,7 +2249,7 @@
       <c r="AQ24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>1991-05</t>
         </is>
@@ -2310,7 +2298,7 @@
       <c r="AQ25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>1991-06</t>
         </is>
@@ -2359,7 +2347,7 @@
       <c r="AQ26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>1991-07</t>
         </is>
@@ -2408,7 +2396,7 @@
       <c r="AQ27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>1991-08</t>
         </is>
@@ -2493,7 +2481,7 @@
       <c r="AQ28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>1991-09</t>
         </is>
@@ -2578,7 +2566,7 @@
       <c r="AQ29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>1991-10</t>
         </is>
@@ -2663,7 +2651,7 @@
       <c r="AQ30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>1991-11</t>
         </is>
@@ -2712,7 +2700,7 @@
       <c r="AQ31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>1991-12</t>
         </is>
@@ -2761,7 +2749,7 @@
       <c r="AQ32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>1992-01</t>
         </is>
@@ -2846,7 +2834,7 @@
       <c r="AQ33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>1992-02</t>
         </is>
@@ -2931,7 +2919,7 @@
       <c r="AQ34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>1992-03</t>
         </is>
@@ -3016,7 +3004,7 @@
       <c r="AQ35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>1992-04</t>
         </is>
@@ -3099,7 +3087,7 @@
       <c r="AQ36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="inlineStr">
+      <c r="A37" t="inlineStr">
         <is>
           <t>1992-05</t>
         </is>
@@ -3148,7 +3136,7 @@
       <c r="AQ37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>1992-06</t>
         </is>
@@ -3197,7 +3185,7 @@
       <c r="AQ38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="inlineStr">
+      <c r="A39" t="inlineStr">
         <is>
           <t>1992-07</t>
         </is>
@@ -3246,7 +3234,7 @@
       <c r="AQ39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>1992-08</t>
         </is>
@@ -3331,7 +3319,7 @@
       <c r="AQ40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="inlineStr">
+      <c r="A41" t="inlineStr">
         <is>
           <t>1992-09</t>
         </is>
@@ -3416,7 +3404,7 @@
       <c r="AQ41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="inlineStr">
+      <c r="A42" t="inlineStr">
         <is>
           <t>1992-10</t>
         </is>
@@ -3491,7 +3479,7 @@
       <c r="AQ42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="inlineStr">
+      <c r="A43" t="inlineStr">
         <is>
           <t>1992-11</t>
         </is>
@@ -3540,7 +3528,7 @@
       <c r="AQ43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="inlineStr">
+      <c r="A44" t="inlineStr">
         <is>
           <t>1992-12</t>
         </is>
@@ -3589,7 +3577,7 @@
       <c r="AQ44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="inlineStr">
+      <c r="A45" t="inlineStr">
         <is>
           <t>1993-01</t>
         </is>
@@ -3638,7 +3626,7 @@
       <c r="AQ45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="inlineStr">
+      <c r="A46" t="inlineStr">
         <is>
           <t>1993-02</t>
         </is>
@@ -3723,7 +3711,7 @@
       <c r="AQ46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="inlineStr">
+      <c r="A47" t="inlineStr">
         <is>
           <t>1993-03</t>
         </is>
@@ -3808,7 +3796,7 @@
       <c r="AQ47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="inlineStr">
+      <c r="A48" t="inlineStr">
         <is>
           <t>1993-04</t>
         </is>
@@ -3893,7 +3881,7 @@
       <c r="AQ48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="inlineStr">
+      <c r="A49" t="inlineStr">
         <is>
           <t>1993-05</t>
         </is>
@@ -3942,7 +3930,7 @@
       <c r="AQ49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="inlineStr">
+      <c r="A50" t="inlineStr">
         <is>
           <t>1993-06</t>
         </is>
@@ -3991,7 +3979,7 @@
       <c r="AQ50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="inlineStr">
+      <c r="A51" t="inlineStr">
         <is>
           <t>1993-07</t>
         </is>
@@ -4040,7 +4028,7 @@
       <c r="AQ51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="inlineStr">
+      <c r="A52" t="inlineStr">
         <is>
           <t>1993-08</t>
         </is>
@@ -4133,7 +4121,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="inlineStr">
+      <c r="A53" t="inlineStr">
         <is>
           <t>1993-09</t>
         </is>
@@ -4226,7 +4214,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="inlineStr">
+      <c r="A54" t="inlineStr">
         <is>
           <t>1993-10</t>
         </is>
@@ -4303,7 +4291,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="inlineStr">
+      <c r="A55" t="inlineStr">
         <is>
           <t>1993-11</t>
         </is>
@@ -4352,7 +4340,7 @@
       <c r="AQ55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="inlineStr">
+      <c r="A56" t="inlineStr">
         <is>
           <t>1993-12</t>
         </is>
@@ -4401,7 +4389,7 @@
       <c r="AQ56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="inlineStr">
+      <c r="A57" t="inlineStr">
         <is>
           <t>1994-01</t>
         </is>
@@ -4450,7 +4438,7 @@
       <c r="AQ57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="inlineStr">
+      <c r="A58" t="inlineStr">
         <is>
           <t>1994-02</t>
         </is>
@@ -4543,7 +4531,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="inlineStr">
+      <c r="A59" t="inlineStr">
         <is>
           <t>1994-03</t>
         </is>
@@ -4636,7 +4624,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="inlineStr">
+      <c r="A60" t="inlineStr">
         <is>
           <t>1994-04</t>
         </is>
@@ -4729,7 +4717,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="inlineStr">
+      <c r="A61" t="inlineStr">
         <is>
           <t>1994-05</t>
         </is>
@@ -4778,7 +4766,7 @@
       <c r="AQ61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="inlineStr">
+      <c r="A62" t="inlineStr">
         <is>
           <t>1994-06</t>
         </is>
@@ -4827,7 +4815,7 @@
       <c r="AQ62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="inlineStr">
+      <c r="A63" t="inlineStr">
         <is>
           <t>1994-07</t>
         </is>
@@ -4876,7 +4864,7 @@
       <c r="AQ63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="inlineStr">
+      <c r="A64" t="inlineStr">
         <is>
           <t>1994-08</t>
         </is>
@@ -4925,7 +4913,7 @@
       <c r="AQ64" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="inlineStr">
+      <c r="A65" t="inlineStr">
         <is>
           <t>1994-09</t>
         </is>
@@ -5024,7 +5012,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="inlineStr">
+      <c r="A66" t="inlineStr">
         <is>
           <t>1994-10</t>
         </is>
@@ -5123,7 +5111,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="inlineStr">
+      <c r="A67" t="inlineStr">
         <is>
           <t>1994-11</t>
         </is>
@@ -5212,7 +5200,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="inlineStr">
+      <c r="A68" t="inlineStr">
         <is>
           <t>1994-12</t>
         </is>
@@ -5261,7 +5249,7 @@
       <c r="AQ68" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="inlineStr">
+      <c r="A69" t="inlineStr">
         <is>
           <t>1995-01</t>
         </is>
@@ -5310,7 +5298,7 @@
       <c r="AQ69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="inlineStr">
+      <c r="A70" t="inlineStr">
         <is>
           <t>1995-02</t>
         </is>
@@ -5359,7 +5347,7 @@
       <c r="AQ70" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="inlineStr">
+      <c r="A71" t="inlineStr">
         <is>
           <t>1995-03</t>
         </is>
@@ -5458,7 +5446,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="inlineStr">
+      <c r="A72" t="inlineStr">
         <is>
           <t>1995-04</t>
         </is>
@@ -5557,7 +5545,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="inlineStr">
+      <c r="A73" t="inlineStr">
         <is>
           <t>1995-05</t>
         </is>
@@ -5606,7 +5594,7 @@
       <c r="AQ73" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="inlineStr">
+      <c r="A74" t="inlineStr">
         <is>
           <t>1995-06</t>
         </is>
@@ -5655,7 +5643,7 @@
       <c r="AQ74" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="inlineStr">
+      <c r="A75" t="inlineStr">
         <is>
           <t>1995-07</t>
         </is>
@@ -5704,7 +5692,7 @@
       <c r="AQ75" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="inlineStr">
+      <c r="A76" t="inlineStr">
         <is>
           <t>1995-08</t>
         </is>
@@ -5777,7 +5765,7 @@
       <c r="AQ76" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="inlineStr">
+      <c r="A77" t="inlineStr">
         <is>
           <t>1995-09</t>
         </is>
@@ -5876,7 +5864,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="inlineStr">
+      <c r="A78" t="inlineStr">
         <is>
           <t>1995-10</t>
         </is>
@@ -5975,7 +5963,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="inlineStr">
+      <c r="A79" t="inlineStr">
         <is>
           <t>1995-11</t>
         </is>
@@ -6074,7 +6062,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="inlineStr">
+      <c r="A80" t="inlineStr">
         <is>
           <t>1995-12</t>
         </is>
@@ -6123,7 +6111,7 @@
       <c r="AQ80" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="inlineStr">
+      <c r="A81" t="inlineStr">
         <is>
           <t>1996-01</t>
         </is>
@@ -6172,7 +6160,7 @@
       <c r="AQ81" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="inlineStr">
+      <c r="A82" t="inlineStr">
         <is>
           <t>1996-02</t>
         </is>
@@ -6221,7 +6209,7 @@
       <c r="AQ82" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="inlineStr">
+      <c r="A83" t="inlineStr">
         <is>
           <t>1996-03</t>
         </is>
@@ -6320,7 +6308,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="inlineStr">
+      <c r="A84" t="inlineStr">
         <is>
           <t>1996-04</t>
         </is>
@@ -6419,7 +6407,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="inlineStr">
+      <c r="A85" t="inlineStr">
         <is>
           <t>1996-05</t>
         </is>
@@ -6468,7 +6456,7 @@
       <c r="AQ85" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="inlineStr">
+      <c r="A86" t="inlineStr">
         <is>
           <t>1996-06</t>
         </is>
@@ -6517,7 +6505,7 @@
       <c r="AQ86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="inlineStr">
+      <c r="A87" t="inlineStr">
         <is>
           <t>1996-07</t>
         </is>
@@ -6566,7 +6554,7 @@
       <c r="AQ87" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="inlineStr">
+      <c r="A88" t="inlineStr">
         <is>
           <t>1996-08</t>
         </is>
@@ -6665,7 +6653,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="inlineStr">
+      <c r="A89" t="inlineStr">
         <is>
           <t>1996-09</t>
         </is>
@@ -6784,7 +6772,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="inlineStr">
+      <c r="A90" t="inlineStr">
         <is>
           <t>1996-10</t>
         </is>
@@ -6903,7 +6891,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="inlineStr">
+      <c r="A91" t="inlineStr">
         <is>
           <t>1996-11</t>
         </is>
@@ -6972,7 +6960,7 @@
       <c r="AQ91" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="inlineStr">
+      <c r="A92" t="inlineStr">
         <is>
           <t>1996-12</t>
         </is>
@@ -7021,7 +7009,7 @@
       <c r="AQ92" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="inlineStr">
+      <c r="A93" t="inlineStr">
         <is>
           <t>1997-01</t>
         </is>
@@ -7070,7 +7058,7 @@
       <c r="AQ93" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="inlineStr">
+      <c r="A94" t="inlineStr">
         <is>
           <t>1997-02</t>
         </is>
@@ -7119,7 +7107,7 @@
       <c r="AQ94" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="inlineStr">
+      <c r="A95" t="inlineStr">
         <is>
           <t>1997-03</t>
         </is>
@@ -7218,7 +7206,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="inlineStr">
+      <c r="A96" t="inlineStr">
         <is>
           <t>1997-04</t>
         </is>
@@ -7317,7 +7305,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="inlineStr">
+      <c r="A97" t="inlineStr">
         <is>
           <t>1997-05</t>
         </is>
@@ -7366,7 +7354,7 @@
       <c r="AQ97" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="inlineStr">
+      <c r="A98" t="inlineStr">
         <is>
           <t>1997-06</t>
         </is>
@@ -7465,7 +7453,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="inlineStr">
+      <c r="A99" t="inlineStr">
         <is>
           <t>1997-07</t>
         </is>
@@ -7514,7 +7502,7 @@
       <c r="AQ99" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="inlineStr">
+      <c r="A100" t="inlineStr">
         <is>
           <t>1997-08</t>
         </is>
@@ -7563,7 +7551,7 @@
       <c r="AQ100" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="inlineStr">
+      <c r="A101" t="inlineStr">
         <is>
           <t>1997-09</t>
         </is>
@@ -7662,7 +7650,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="inlineStr">
+      <c r="A102" t="inlineStr">
         <is>
           <t>1997-10</t>
         </is>
@@ -7761,7 +7749,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="inlineStr">
+      <c r="A103" t="inlineStr">
         <is>
           <t>1997-11</t>
         </is>
@@ -7810,7 +7798,7 @@
       <c r="AQ103" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="inlineStr">
+      <c r="A104" t="inlineStr">
         <is>
           <t>1997-12</t>
         </is>
@@ -7859,7 +7847,7 @@
       <c r="AQ104" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="inlineStr">
+      <c r="A105" t="inlineStr">
         <is>
           <t>1998-01</t>
         </is>
@@ -7908,7 +7896,7 @@
       <c r="AQ105" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="inlineStr">
+      <c r="A106" t="inlineStr">
         <is>
           <t>1998-02</t>
         </is>
@@ -7957,7 +7945,7 @@
       <c r="AQ106" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="inlineStr">
+      <c r="A107" t="inlineStr">
         <is>
           <t>1998-03</t>
         </is>
@@ -8058,7 +8046,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="inlineStr">
+      <c r="A108" t="inlineStr">
         <is>
           <t>1998-04</t>
         </is>
@@ -8159,7 +8147,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="inlineStr">
+      <c r="A109" t="inlineStr">
         <is>
           <t>1998-05</t>
         </is>
@@ -8260,7 +8248,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="inlineStr">
+      <c r="A110" t="inlineStr">
         <is>
           <t>1998-06</t>
         </is>
@@ -8309,7 +8297,7 @@
       <c r="AQ110" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="inlineStr">
+      <c r="A111" t="inlineStr">
         <is>
           <t>1998-07</t>
         </is>
@@ -8358,7 +8346,7 @@
       <c r="AQ111" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="inlineStr">
+      <c r="A112" t="inlineStr">
         <is>
           <t>1998-08</t>
         </is>
@@ -8407,7 +8395,7 @@
       <c r="AQ112" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="inlineStr">
+      <c r="A113" t="inlineStr">
         <is>
           <t>1998-09</t>
         </is>
@@ -8508,7 +8496,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="inlineStr">
+      <c r="A114" t="inlineStr">
         <is>
           <t>1998-10</t>
         </is>
@@ -8609,7 +8597,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="inlineStr">
+      <c r="A115" t="inlineStr">
         <is>
           <t>1998-11</t>
         </is>
@@ -8710,7 +8698,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="inlineStr">
+      <c r="A116" t="inlineStr">
         <is>
           <t>1998-12</t>
         </is>
@@ -8797,7 +8785,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="inlineStr">
+      <c r="A117" t="inlineStr">
         <is>
           <t>1999-01</t>
         </is>
@@ -8918,7 +8906,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="inlineStr">
+      <c r="A118" t="inlineStr">
         <is>
           <t>1999-02</t>
         </is>
@@ -9051,7 +9039,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="inlineStr">
+      <c r="A119" t="inlineStr">
         <is>
           <t>1999-03</t>
         </is>
@@ -9184,7 +9172,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="inlineStr">
+      <c r="A120" t="inlineStr">
         <is>
           <t>1999-04</t>
         </is>
@@ -9317,7 +9305,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="inlineStr">
+      <c r="A121" t="inlineStr">
         <is>
           <t>1999-05</t>
         </is>
@@ -9450,7 +9438,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="inlineStr">
+      <c r="A122" t="inlineStr">
         <is>
           <t>1999-06</t>
         </is>
@@ -9583,7 +9571,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="inlineStr">
+      <c r="A123" t="inlineStr">
         <is>
           <t>1999-07</t>
         </is>
@@ -9716,7 +9704,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="inlineStr">
+      <c r="A124" t="inlineStr">
         <is>
           <t>1999-08</t>
         </is>
@@ -9849,7 +9837,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="inlineStr">
+      <c r="A125" t="inlineStr">
         <is>
           <t>1999-09</t>
         </is>
@@ -9982,7 +9970,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="inlineStr">
+      <c r="A126" t="inlineStr">
         <is>
           <t>1999-10</t>
         </is>
@@ -10115,7 +10103,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="inlineStr">
+      <c r="A127" t="inlineStr">
         <is>
           <t>1999-11</t>
         </is>
@@ -10248,7 +10236,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="inlineStr">
+      <c r="A128" t="inlineStr">
         <is>
           <t>1999-12</t>
         </is>
@@ -10379,7 +10367,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="inlineStr">
+      <c r="A129" t="inlineStr">
         <is>
           <t>2000-01</t>
         </is>
@@ -10512,7 +10500,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="inlineStr">
+      <c r="A130" t="inlineStr">
         <is>
           <t>2000-02</t>
         </is>
@@ -10645,7 +10633,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="inlineStr">
+      <c r="A131" t="inlineStr">
         <is>
           <t>2000-03</t>
         </is>
@@ -10778,7 +10766,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="inlineStr">
+      <c r="A132" t="inlineStr">
         <is>
           <t>2000-04</t>
         </is>
@@ -10871,7 +10859,7 @@
       <c r="AQ132" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="inlineStr">
+      <c r="A133" t="inlineStr">
         <is>
           <t>2000-05</t>
         </is>
@@ -11004,7 +10992,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="inlineStr">
+      <c r="A134" t="inlineStr">
         <is>
           <t>2000-06</t>
         </is>
@@ -11137,7 +11125,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="inlineStr">
+      <c r="A135" t="inlineStr">
         <is>
           <t>2000-07</t>
         </is>
@@ -11270,7 +11258,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="inlineStr">
+      <c r="A136" t="inlineStr">
         <is>
           <t>2000-08</t>
         </is>
@@ -11403,7 +11391,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="inlineStr">
+      <c r="A137" t="inlineStr">
         <is>
           <t>2000-09</t>
         </is>
@@ -11452,7 +11440,7 @@
       <c r="AQ137" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="inlineStr">
+      <c r="A138" t="inlineStr">
         <is>
           <t>2000-10</t>
         </is>
@@ -11501,7 +11489,7 @@
       <c r="AQ138" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="inlineStr">
+      <c r="A139" t="inlineStr">
         <is>
           <t>2000-11</t>
         </is>
@@ -11550,7 +11538,7 @@
       <c r="AQ139" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="inlineStr">
+      <c r="A140" t="inlineStr">
         <is>
           <t>2000-12</t>
         </is>
@@ -11599,7 +11587,7 @@
       <c r="AQ140" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="inlineStr">
+      <c r="A141" t="inlineStr">
         <is>
           <t>2001-01</t>
         </is>
@@ -11702,7 +11690,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="inlineStr">
+      <c r="A142" t="inlineStr">
         <is>
           <t>2001-02</t>
         </is>
@@ -11751,7 +11739,7 @@
       <c r="AQ142" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="inlineStr">
+      <c r="A143" t="inlineStr">
         <is>
           <t>2001-03</t>
         </is>
@@ -11800,7 +11788,7 @@
       <c r="AQ143" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="inlineStr">
+      <c r="A144" t="inlineStr">
         <is>
           <t>2001-04</t>
         </is>
@@ -11933,7 +11921,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="inlineStr">
+      <c r="A145" t="inlineStr">
         <is>
           <t>2001-05</t>
         </is>
@@ -12066,7 +12054,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="inlineStr">
+      <c r="A146" t="inlineStr">
         <is>
           <t>2001-06</t>
         </is>
@@ -12199,7 +12187,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="inlineStr">
+      <c r="A147" t="inlineStr">
         <is>
           <t>2001-07</t>
         </is>
@@ -12330,7 +12318,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="inlineStr">
+      <c r="A148" t="inlineStr">
         <is>
           <t>2001-08</t>
         </is>
@@ -12463,7 +12451,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="inlineStr">
+      <c r="A149" t="inlineStr">
         <is>
           <t>2001-09</t>
         </is>
@@ -12592,7 +12580,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="inlineStr">
+      <c r="A150" t="inlineStr">
         <is>
           <t>2001-10</t>
         </is>
@@ -12725,7 +12713,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="inlineStr">
+      <c r="A151" t="inlineStr">
         <is>
           <t>2001-11</t>
         </is>
@@ -12858,7 +12846,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="inlineStr">
+      <c r="A152" t="inlineStr">
         <is>
           <t>2001-12</t>
         </is>
@@ -12991,7 +12979,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="inlineStr">
+      <c r="A153" t="inlineStr">
         <is>
           <t>2002-01</t>
         </is>
@@ -13124,7 +13112,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="inlineStr">
+      <c r="A154" t="inlineStr">
         <is>
           <t>2002-02</t>
         </is>
@@ -13257,7 +13245,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="inlineStr">
+      <c r="A155" t="inlineStr">
         <is>
           <t>2002-03</t>
         </is>
@@ -13390,7 +13378,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="inlineStr">
+      <c r="A156" t="inlineStr">
         <is>
           <t>2002-04</t>
         </is>
@@ -13523,7 +13511,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="inlineStr">
+      <c r="A157" t="inlineStr">
         <is>
           <t>2002-05</t>
         </is>
@@ -13656,7 +13644,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="inlineStr">
+      <c r="A158" t="inlineStr">
         <is>
           <t>2002-06</t>
         </is>
@@ -13789,7 +13777,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="inlineStr">
+      <c r="A159" t="inlineStr">
         <is>
           <t>2002-07</t>
         </is>
@@ -13922,7 +13910,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="inlineStr">
+      <c r="A160" t="inlineStr">
         <is>
           <t>2002-08</t>
         </is>
@@ -14055,7 +14043,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="inlineStr">
+      <c r="A161" t="inlineStr">
         <is>
           <t>2002-09</t>
         </is>
@@ -14188,7 +14176,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="inlineStr">
+      <c r="A162" t="inlineStr">
         <is>
           <t>2002-10</t>
         </is>
@@ -14321,7 +14309,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="inlineStr">
+      <c r="A163" t="inlineStr">
         <is>
           <t>2002-11</t>
         </is>
@@ -14454,7 +14442,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="inlineStr">
+      <c r="A164" t="inlineStr">
         <is>
           <t>2002-12</t>
         </is>
@@ -14587,7 +14575,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="inlineStr">
+      <c r="A165" t="inlineStr">
         <is>
           <t>2003-01</t>
         </is>
@@ -14720,7 +14708,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="inlineStr">
+      <c r="A166" t="inlineStr">
         <is>
           <t>2003-02</t>
         </is>
@@ -14853,7 +14841,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="inlineStr">
+      <c r="A167" t="inlineStr">
         <is>
           <t>2003-03</t>
         </is>
@@ -14986,7 +14974,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="inlineStr">
+      <c r="A168" t="inlineStr">
         <is>
           <t>2003-04</t>
         </is>
@@ -15119,7 +15107,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="inlineStr">
+      <c r="A169" t="inlineStr">
         <is>
           <t>2003-05</t>
         </is>
@@ -15252,7 +15240,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="inlineStr">
+      <c r="A170" t="inlineStr">
         <is>
           <t>2003-06</t>
         </is>
@@ -15385,7 +15373,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="inlineStr">
+      <c r="A171" t="inlineStr">
         <is>
           <t>2003-07</t>
         </is>
@@ -15518,7 +15506,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="inlineStr">
+      <c r="A172" t="inlineStr">
         <is>
           <t>2003-08</t>
         </is>
@@ -15651,7 +15639,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="inlineStr">
+      <c r="A173" t="inlineStr">
         <is>
           <t>2003-09</t>
         </is>
@@ -15784,7 +15772,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="inlineStr">
+      <c r="A174" t="inlineStr">
         <is>
           <t>2003-10</t>
         </is>
@@ -15917,7 +15905,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="inlineStr">
+      <c r="A175" t="inlineStr">
         <is>
           <t>2003-11</t>
         </is>
@@ -16050,7 +16038,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="inlineStr">
+      <c r="A176" t="inlineStr">
         <is>
           <t>2003-12</t>
         </is>
@@ -16183,7 +16171,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="inlineStr">
+      <c r="A177" t="inlineStr">
         <is>
           <t>2004-01</t>
         </is>
@@ -16316,7 +16304,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="inlineStr">
+      <c r="A178" t="inlineStr">
         <is>
           <t>2004-02</t>
         </is>
@@ -16449,7 +16437,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="inlineStr">
+      <c r="A179" t="inlineStr">
         <is>
           <t>2004-03</t>
         </is>
@@ -16582,7 +16570,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="inlineStr">
+      <c r="A180" t="inlineStr">
         <is>
           <t>2004-04</t>
         </is>
@@ -16715,7 +16703,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="inlineStr">
+      <c r="A181" t="inlineStr">
         <is>
           <t>2004-05</t>
         </is>
@@ -16848,7 +16836,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="inlineStr">
+      <c r="A182" t="inlineStr">
         <is>
           <t>2004-06</t>
         </is>
@@ -16981,7 +16969,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="inlineStr">
+      <c r="A183" t="inlineStr">
         <is>
           <t>2004-07</t>
         </is>
@@ -17114,7 +17102,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="inlineStr">
+      <c r="A184" t="inlineStr">
         <is>
           <t>2004-08</t>
         </is>
@@ -17247,7 +17235,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="inlineStr">
+      <c r="A185" t="inlineStr">
         <is>
           <t>2004-09</t>
         </is>
@@ -17380,7 +17368,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="inlineStr">
+      <c r="A186" t="inlineStr">
         <is>
           <t>2004-10</t>
         </is>
@@ -17513,7 +17501,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="inlineStr">
+      <c r="A187" t="inlineStr">
         <is>
           <t>2004-11</t>
         </is>
@@ -17646,7 +17634,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="inlineStr">
+      <c r="A188" t="inlineStr">
         <is>
           <t>2004-12</t>
         </is>
@@ -17779,7 +17767,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="inlineStr">
+      <c r="A189" t="inlineStr">
         <is>
           <t>2005-01</t>
         </is>
@@ -17912,7 +17900,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="inlineStr">
+      <c r="A190" t="inlineStr">
         <is>
           <t>2005-02</t>
         </is>
@@ -18045,7 +18033,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="inlineStr">
+      <c r="A191" t="inlineStr">
         <is>
           <t>2005-03</t>
         </is>
@@ -18178,7 +18166,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="inlineStr">
+      <c r="A192" t="inlineStr">
         <is>
           <t>2005-04</t>
         </is>
@@ -18311,7 +18299,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="inlineStr">
+      <c r="A193" t="inlineStr">
         <is>
           <t>2005-05</t>
         </is>
@@ -18444,7 +18432,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="inlineStr">
+      <c r="A194" t="inlineStr">
         <is>
           <t>2005-06</t>
         </is>
@@ -18577,7 +18565,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="inlineStr">
+      <c r="A195" t="inlineStr">
         <is>
           <t>2005-07</t>
         </is>
@@ -18710,7 +18698,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="inlineStr">
+      <c r="A196" t="inlineStr">
         <is>
           <t>2005-08</t>
         </is>
@@ -18843,7 +18831,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="inlineStr">
+      <c r="A197" t="inlineStr">
         <is>
           <t>2005-09</t>
         </is>
@@ -18976,7 +18964,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="inlineStr">
+      <c r="A198" t="inlineStr">
         <is>
           <t>2005-10</t>
         </is>
@@ -19109,7 +19097,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="inlineStr">
+      <c r="A199" t="inlineStr">
         <is>
           <t>2005-11</t>
         </is>
@@ -19242,7 +19230,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="inlineStr">
+      <c r="A200" t="inlineStr">
         <is>
           <t>2005-12</t>
         </is>
@@ -19375,7 +19363,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="inlineStr">
+      <c r="A201" t="inlineStr">
         <is>
           <t>2006-01</t>
         </is>
@@ -19508,7 +19496,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="inlineStr">
+      <c r="A202" t="inlineStr">
         <is>
           <t>2006-02</t>
         </is>
@@ -19641,7 +19629,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="inlineStr">
+      <c r="A203" t="inlineStr">
         <is>
           <t>2006-03</t>
         </is>
@@ -19774,7 +19762,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="inlineStr">
+      <c r="A204" t="inlineStr">
         <is>
           <t>2006-04</t>
         </is>
@@ -19907,7 +19895,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="inlineStr">
+      <c r="A205" t="inlineStr">
         <is>
           <t>2006-05</t>
         </is>
@@ -20040,7 +20028,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="inlineStr">
+      <c r="A206" t="inlineStr">
         <is>
           <t>2006-06</t>
         </is>
@@ -20173,7 +20161,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="inlineStr">
+      <c r="A207" t="inlineStr">
         <is>
           <t>2006-07</t>
         </is>
@@ -20306,7 +20294,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="inlineStr">
+      <c r="A208" t="inlineStr">
         <is>
           <t>2006-08</t>
         </is>
@@ -20439,7 +20427,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="inlineStr">
+      <c r="A209" t="inlineStr">
         <is>
           <t>2006-09</t>
         </is>
@@ -20572,7 +20560,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="inlineStr">
+      <c r="A210" t="inlineStr">
         <is>
           <t>2006-10</t>
         </is>
@@ -20705,7 +20693,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="inlineStr">
+      <c r="A211" t="inlineStr">
         <is>
           <t>2006-11</t>
         </is>
@@ -20838,7 +20826,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="inlineStr">
+      <c r="A212" t="inlineStr">
         <is>
           <t>2006-12</t>
         </is>
@@ -20971,7 +20959,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="inlineStr">
+      <c r="A213" t="inlineStr">
         <is>
           <t>2007-01</t>
         </is>
@@ -21104,7 +21092,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="inlineStr">
+      <c r="A214" t="inlineStr">
         <is>
           <t>2007-02</t>
         </is>
@@ -21237,7 +21225,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="inlineStr">
+      <c r="A215" t="inlineStr">
         <is>
           <t>2007-03</t>
         </is>
@@ -21370,7 +21358,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="inlineStr">
+      <c r="A216" t="inlineStr">
         <is>
           <t>2007-04</t>
         </is>
@@ -21503,7 +21491,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="inlineStr">
+      <c r="A217" t="inlineStr">
         <is>
           <t>2007-05</t>
         </is>
@@ -21636,7 +21624,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="inlineStr">
+      <c r="A218" t="inlineStr">
         <is>
           <t>2007-06</t>
         </is>
@@ -21769,7 +21757,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="inlineStr">
+      <c r="A219" t="inlineStr">
         <is>
           <t>2007-07</t>
         </is>
@@ -21902,7 +21890,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="inlineStr">
+      <c r="A220" t="inlineStr">
         <is>
           <t>2007-08</t>
         </is>
@@ -22035,7 +22023,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="inlineStr">
+      <c r="A221" t="inlineStr">
         <is>
           <t>2007-09</t>
         </is>
@@ -22168,7 +22156,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="inlineStr">
+      <c r="A222" t="inlineStr">
         <is>
           <t>2007-10</t>
         </is>
@@ -22301,7 +22289,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="inlineStr">
+      <c r="A223" t="inlineStr">
         <is>
           <t>2007-11</t>
         </is>
@@ -22434,7 +22422,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="inlineStr">
+      <c r="A224" t="inlineStr">
         <is>
           <t>2007-12</t>
         </is>
@@ -22567,7 +22555,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="inlineStr">
+      <c r="A225" t="inlineStr">
         <is>
           <t>2008-01</t>
         </is>
@@ -22700,7 +22688,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="inlineStr">
+      <c r="A226" t="inlineStr">
         <is>
           <t>2008-02</t>
         </is>
@@ -22833,7 +22821,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="inlineStr">
+      <c r="A227" t="inlineStr">
         <is>
           <t>2008-03</t>
         </is>
@@ -22966,7 +22954,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="inlineStr">
+      <c r="A228" t="inlineStr">
         <is>
           <t>2008-04</t>
         </is>
@@ -23099,7 +23087,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="inlineStr">
+      <c r="A229" t="inlineStr">
         <is>
           <t>2008-05</t>
         </is>
@@ -23232,7 +23220,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="inlineStr">
+      <c r="A230" t="inlineStr">
         <is>
           <t>2008-06</t>
         </is>
@@ -23365,7 +23353,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="inlineStr">
+      <c r="A231" t="inlineStr">
         <is>
           <t>2008-07</t>
         </is>
@@ -23498,7 +23486,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="inlineStr">
+      <c r="A232" t="inlineStr">
         <is>
           <t>2008-08</t>
         </is>
@@ -23631,7 +23619,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="inlineStr">
+      <c r="A233" t="inlineStr">
         <is>
           <t>2008-09</t>
         </is>
@@ -23762,7 +23750,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="inlineStr">
+      <c r="A234" t="inlineStr">
         <is>
           <t>2008-10</t>
         </is>
@@ -23895,7 +23883,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="inlineStr">
+      <c r="A235" t="inlineStr">
         <is>
           <t>2008-11</t>
         </is>
@@ -24028,7 +24016,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="inlineStr">
+      <c r="A236" t="inlineStr">
         <is>
           <t>2008-12</t>
         </is>
@@ -24161,7 +24149,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="inlineStr">
+      <c r="A237" t="inlineStr">
         <is>
           <t>2009-01</t>
         </is>
@@ -24294,7 +24282,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="inlineStr">
+      <c r="A238" t="inlineStr">
         <is>
           <t>2009-02</t>
         </is>
@@ -24427,7 +24415,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="inlineStr">
+      <c r="A239" t="inlineStr">
         <is>
           <t>2009-03</t>
         </is>
@@ -24560,7 +24548,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="inlineStr">
+      <c r="A240" t="inlineStr">
         <is>
           <t>2009-04</t>
         </is>
@@ -24609,7 +24597,7 @@
       <c r="AQ240" t="inlineStr"/>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="inlineStr">
+      <c r="A241" t="inlineStr">
         <is>
           <t>2009-05</t>
         </is>
@@ -24742,7 +24730,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="inlineStr">
+      <c r="A242" t="inlineStr">
         <is>
           <t>2009-06</t>
         </is>
@@ -24875,7 +24863,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="inlineStr">
+      <c r="A243" t="inlineStr">
         <is>
           <t>2009-07</t>
         </is>
@@ -25008,7 +24996,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="inlineStr">
+      <c r="A244" t="inlineStr">
         <is>
           <t>2009-08</t>
         </is>
@@ -25141,7 +25129,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="inlineStr">
+      <c r="A245" t="inlineStr">
         <is>
           <t>2009-09</t>
         </is>
@@ -25274,7 +25262,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="inlineStr">
+      <c r="A246" t="inlineStr">
         <is>
           <t>2009-10</t>
         </is>
@@ -25407,7 +25395,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="inlineStr">
+      <c r="A247" t="inlineStr">
         <is>
           <t>2009-11</t>
         </is>
@@ -25540,7 +25528,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="inlineStr">
+      <c r="A248" t="inlineStr">
         <is>
           <t>2009-12</t>
         </is>
@@ -25673,7 +25661,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="inlineStr">
+      <c r="A249" t="inlineStr">
         <is>
           <t>2010-01</t>
         </is>
@@ -25806,7 +25794,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="inlineStr">
+      <c r="A250" t="inlineStr">
         <is>
           <t>2010-02</t>
         </is>
@@ -25939,7 +25927,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="1" t="inlineStr">
+      <c r="A251" t="inlineStr">
         <is>
           <t>2010-03</t>
         </is>
@@ -26072,7 +26060,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="1" t="inlineStr">
+      <c r="A252" t="inlineStr">
         <is>
           <t>2010-04</t>
         </is>
@@ -26205,7 +26193,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="1" t="inlineStr">
+      <c r="A253" t="inlineStr">
         <is>
           <t>2010-05</t>
         </is>
@@ -26338,7 +26326,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="1" t="inlineStr">
+      <c r="A254" t="inlineStr">
         <is>
           <t>2010-06</t>
         </is>
@@ -26471,7 +26459,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="1" t="inlineStr">
+      <c r="A255" t="inlineStr">
         <is>
           <t>2010-07</t>
         </is>
@@ -26604,7 +26592,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="1" t="inlineStr">
+      <c r="A256" t="inlineStr">
         <is>
           <t>2010-08</t>
         </is>
@@ -26737,7 +26725,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="1" t="inlineStr">
+      <c r="A257" t="inlineStr">
         <is>
           <t>2010-09</t>
         </is>
@@ -26870,7 +26858,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="1" t="inlineStr">
+      <c r="A258" t="inlineStr">
         <is>
           <t>2010-10</t>
         </is>
@@ -27003,7 +26991,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="1" t="inlineStr">
+      <c r="A259" t="inlineStr">
         <is>
           <t>2010-11</t>
         </is>
@@ -27136,7 +27124,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="1" t="inlineStr">
+      <c r="A260" t="inlineStr">
         <is>
           <t>2010-12</t>
         </is>
@@ -27269,7 +27257,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="1" t="inlineStr">
+      <c r="A261" t="inlineStr">
         <is>
           <t>2011-01</t>
         </is>
@@ -27318,7 +27306,7 @@
       <c r="AQ261" t="inlineStr"/>
     </row>
     <row r="262">
-      <c r="A262" s="1" t="inlineStr">
+      <c r="A262" t="inlineStr">
         <is>
           <t>2011-02</t>
         </is>
@@ -27451,7 +27439,7 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="1" t="inlineStr">
+      <c r="A263" t="inlineStr">
         <is>
           <t>2011-03</t>
         </is>
@@ -27584,7 +27572,7 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="1" t="inlineStr">
+      <c r="A264" t="inlineStr">
         <is>
           <t>2011-04</t>
         </is>
@@ -27717,7 +27705,7 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="1" t="inlineStr">
+      <c r="A265" t="inlineStr">
         <is>
           <t>2011-05</t>
         </is>
@@ -27850,7 +27838,7 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="1" t="inlineStr">
+      <c r="A266" t="inlineStr">
         <is>
           <t>2011-06</t>
         </is>
@@ -27983,7 +27971,7 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="1" t="inlineStr">
+      <c r="A267" t="inlineStr">
         <is>
           <t>2011-07</t>
         </is>
@@ -28116,7 +28104,7 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="1" t="inlineStr">
+      <c r="A268" t="inlineStr">
         <is>
           <t>2011-08</t>
         </is>
@@ -28249,7 +28237,7 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="1" t="inlineStr">
+      <c r="A269" t="inlineStr">
         <is>
           <t>2011-09</t>
         </is>
@@ -28382,7 +28370,7 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="1" t="inlineStr">
+      <c r="A270" t="inlineStr">
         <is>
           <t>2011-10</t>
         </is>
@@ -28515,7 +28503,7 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="1" t="inlineStr">
+      <c r="A271" t="inlineStr">
         <is>
           <t>2011-11</t>
         </is>
@@ -28648,7 +28636,7 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="1" t="inlineStr">
+      <c r="A272" t="inlineStr">
         <is>
           <t>2011-12</t>
         </is>
@@ -28781,7 +28769,7 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="1" t="inlineStr">
+      <c r="A273" t="inlineStr">
         <is>
           <t>2012-01</t>
         </is>
@@ -28914,7 +28902,7 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="1" t="inlineStr">
+      <c r="A274" t="inlineStr">
         <is>
           <t>2012-02</t>
         </is>
@@ -29047,7 +29035,7 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="1" t="inlineStr">
+      <c r="A275" t="inlineStr">
         <is>
           <t>2012-03</t>
         </is>
@@ -29180,7 +29168,7 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="1" t="inlineStr">
+      <c r="A276" t="inlineStr">
         <is>
           <t>2012-04</t>
         </is>
@@ -29313,7 +29301,7 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="1" t="inlineStr">
+      <c r="A277" t="inlineStr">
         <is>
           <t>2012-05</t>
         </is>
@@ -29446,7 +29434,7 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="1" t="inlineStr">
+      <c r="A278" t="inlineStr">
         <is>
           <t>2012-06</t>
         </is>
@@ -29579,7 +29567,7 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="1" t="inlineStr">
+      <c r="A279" t="inlineStr">
         <is>
           <t>2012-07</t>
         </is>
@@ -29712,7 +29700,7 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="1" t="inlineStr">
+      <c r="A280" t="inlineStr">
         <is>
           <t>2012-08</t>
         </is>
@@ -29845,7 +29833,7 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="1" t="inlineStr">
+      <c r="A281" t="inlineStr">
         <is>
           <t>2012-09</t>
         </is>
@@ -29978,7 +29966,7 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="1" t="inlineStr">
+      <c r="A282" t="inlineStr">
         <is>
           <t>2012-10</t>
         </is>
@@ -30111,7 +30099,7 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="1" t="inlineStr">
+      <c r="A283" t="inlineStr">
         <is>
           <t>2012-11</t>
         </is>
@@ -30244,7 +30232,7 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="1" t="inlineStr">
+      <c r="A284" t="inlineStr">
         <is>
           <t>2012-12</t>
         </is>
@@ -30377,7 +30365,7 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="1" t="inlineStr">
+      <c r="A285" t="inlineStr">
         <is>
           <t>2013-01</t>
         </is>
@@ -30510,7 +30498,7 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="1" t="inlineStr">
+      <c r="A286" t="inlineStr">
         <is>
           <t>2013-02</t>
         </is>
@@ -30643,7 +30631,7 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="1" t="inlineStr">
+      <c r="A287" t="inlineStr">
         <is>
           <t>2013-03</t>
         </is>
@@ -30776,7 +30764,7 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="1" t="inlineStr">
+      <c r="A288" t="inlineStr">
         <is>
           <t>2013-04</t>
         </is>
@@ -30909,7 +30897,7 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="1" t="inlineStr">
+      <c r="A289" t="inlineStr">
         <is>
           <t>2013-05</t>
         </is>
@@ -31042,7 +31030,7 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="1" t="inlineStr">
+      <c r="A290" t="inlineStr">
         <is>
           <t>2013-06</t>
         </is>
@@ -31175,7 +31163,7 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="1" t="inlineStr">
+      <c r="A291" t="inlineStr">
         <is>
           <t>2013-07</t>
         </is>
@@ -31308,7 +31296,7 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="1" t="inlineStr">
+      <c r="A292" t="inlineStr">
         <is>
           <t>2013-08</t>
         </is>
@@ -31441,7 +31429,7 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="1" t="inlineStr">
+      <c r="A293" t="inlineStr">
         <is>
           <t>2013-09</t>
         </is>
@@ -31574,7 +31562,7 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="1" t="inlineStr">
+      <c r="A294" t="inlineStr">
         <is>
           <t>2013-10</t>
         </is>
@@ -31707,7 +31695,7 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="1" t="inlineStr">
+      <c r="A295" t="inlineStr">
         <is>
           <t>2013-11</t>
         </is>
@@ -31840,7 +31828,7 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="1" t="inlineStr">
+      <c r="A296" t="inlineStr">
         <is>
           <t>2013-12</t>
         </is>
@@ -31973,7 +31961,7 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="1" t="inlineStr">
+      <c r="A297" t="inlineStr">
         <is>
           <t>2014-01</t>
         </is>
@@ -32106,7 +32094,7 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="1" t="inlineStr">
+      <c r="A298" t="inlineStr">
         <is>
           <t>2014-02</t>
         </is>
@@ -32239,7 +32227,7 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="1" t="inlineStr">
+      <c r="A299" t="inlineStr">
         <is>
           <t>2014-03</t>
         </is>
@@ -32372,7 +32360,7 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="1" t="inlineStr">
+      <c r="A300" t="inlineStr">
         <is>
           <t>2014-04</t>
         </is>
@@ -32505,7 +32493,7 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="1" t="inlineStr">
+      <c r="A301" t="inlineStr">
         <is>
           <t>2014-05</t>
         </is>
@@ -32638,7 +32626,7 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="1" t="inlineStr">
+      <c r="A302" t="inlineStr">
         <is>
           <t>2014-06</t>
         </is>
@@ -32771,7 +32759,7 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="1" t="inlineStr">
+      <c r="A303" t="inlineStr">
         <is>
           <t>2014-07</t>
         </is>
@@ -32904,7 +32892,7 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="1" t="inlineStr">
+      <c r="A304" t="inlineStr">
         <is>
           <t>2014-08</t>
         </is>
@@ -33037,7 +33025,7 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="1" t="inlineStr">
+      <c r="A305" t="inlineStr">
         <is>
           <t>2014-09</t>
         </is>
@@ -33170,7 +33158,7 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="1" t="inlineStr">
+      <c r="A306" t="inlineStr">
         <is>
           <t>2014-10</t>
         </is>
@@ -33303,7 +33291,7 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="1" t="inlineStr">
+      <c r="A307" t="inlineStr">
         <is>
           <t>2014-11</t>
         </is>
@@ -33436,7 +33424,7 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="1" t="inlineStr">
+      <c r="A308" t="inlineStr">
         <is>
           <t>2014-12</t>
         </is>
@@ -33569,7 +33557,7 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="1" t="inlineStr">
+      <c r="A309" t="inlineStr">
         <is>
           <t>2015-01</t>
         </is>
@@ -33702,7 +33690,7 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="1" t="inlineStr">
+      <c r="A310" t="inlineStr">
         <is>
           <t>2015-02</t>
         </is>
@@ -33835,7 +33823,7 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="1" t="inlineStr">
+      <c r="A311" t="inlineStr">
         <is>
           <t>2015-03</t>
         </is>
@@ -33968,7 +33956,7 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="1" t="inlineStr">
+      <c r="A312" t="inlineStr">
         <is>
           <t>2015-04</t>
         </is>
@@ -34101,7 +34089,7 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="1" t="inlineStr">
+      <c r="A313" t="inlineStr">
         <is>
           <t>2015-05</t>
         </is>
@@ -34234,7 +34222,7 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="1" t="inlineStr">
+      <c r="A314" t="inlineStr">
         <is>
           <t>2015-06</t>
         </is>
@@ -34367,7 +34355,7 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="1" t="inlineStr">
+      <c r="A315" t="inlineStr">
         <is>
           <t>2015-07</t>
         </is>
@@ -34500,7 +34488,7 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="1" t="inlineStr">
+      <c r="A316" t="inlineStr">
         <is>
           <t>2015-08</t>
         </is>
@@ -34633,7 +34621,7 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="1" t="inlineStr">
+      <c r="A317" t="inlineStr">
         <is>
           <t>2015-09</t>
         </is>
@@ -34766,7 +34754,7 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="1" t="inlineStr">
+      <c r="A318" t="inlineStr">
         <is>
           <t>2015-10</t>
         </is>
@@ -34899,7 +34887,7 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="1" t="inlineStr">
+      <c r="A319" t="inlineStr">
         <is>
           <t>2015-11</t>
         </is>
@@ -35032,7 +35020,7 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="1" t="inlineStr">
+      <c r="A320" t="inlineStr">
         <is>
           <t>2015-12</t>
         </is>
@@ -35165,7 +35153,7 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="1" t="inlineStr">
+      <c r="A321" t="inlineStr">
         <is>
           <t>2016-01</t>
         </is>
@@ -35298,7 +35286,7 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="1" t="inlineStr">
+      <c r="A322" t="inlineStr">
         <is>
           <t>2016-02</t>
         </is>
@@ -35431,7 +35419,7 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="1" t="inlineStr">
+      <c r="A323" t="inlineStr">
         <is>
           <t>2016-03</t>
         </is>
@@ -35564,7 +35552,7 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="1" t="inlineStr">
+      <c r="A324" t="inlineStr">
         <is>
           <t>2016-04</t>
         </is>
@@ -35697,7 +35685,7 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="1" t="inlineStr">
+      <c r="A325" t="inlineStr">
         <is>
           <t>2016-05</t>
         </is>
@@ -35830,7 +35818,7 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="1" t="inlineStr">
+      <c r="A326" t="inlineStr">
         <is>
           <t>2016-06</t>
         </is>
@@ -35963,7 +35951,7 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="1" t="inlineStr">
+      <c r="A327" t="inlineStr">
         <is>
           <t>2016-07</t>
         </is>
@@ -36096,7 +36084,7 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="1" t="inlineStr">
+      <c r="A328" t="inlineStr">
         <is>
           <t>2016-08</t>
         </is>
@@ -36229,7 +36217,7 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="1" t="inlineStr">
+      <c r="A329" t="inlineStr">
         <is>
           <t>2016-09</t>
         </is>
@@ -36362,7 +36350,7 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="1" t="inlineStr">
+      <c r="A330" t="inlineStr">
         <is>
           <t>2016-10</t>
         </is>
@@ -36495,7 +36483,7 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="1" t="inlineStr">
+      <c r="A331" t="inlineStr">
         <is>
           <t>2016-11</t>
         </is>
@@ -36628,7 +36616,7 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="1" t="inlineStr">
+      <c r="A332" t="inlineStr">
         <is>
           <t>2016-12</t>
         </is>
@@ -36761,7 +36749,7 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="1" t="inlineStr">
+      <c r="A333" t="inlineStr">
         <is>
           <t>2017-01</t>
         </is>
@@ -36894,7 +36882,7 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="1" t="inlineStr">
+      <c r="A334" t="inlineStr">
         <is>
           <t>2017-02</t>
         </is>
@@ -37027,7 +37015,7 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" s="1" t="inlineStr">
+      <c r="A335" t="inlineStr">
         <is>
           <t>2017-03</t>
         </is>
@@ -37160,7 +37148,7 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="1" t="inlineStr">
+      <c r="A336" t="inlineStr">
         <is>
           <t>2017-04</t>
         </is>
@@ -37293,7 +37281,7 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="1" t="inlineStr">
+      <c r="A337" t="inlineStr">
         <is>
           <t>2017-05</t>
         </is>
@@ -37426,7 +37414,7 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="1" t="inlineStr">
+      <c r="A338" t="inlineStr">
         <is>
           <t>2017-06</t>
         </is>
@@ -37559,7 +37547,7 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="1" t="inlineStr">
+      <c r="A339" t="inlineStr">
         <is>
           <t>2017-07</t>
         </is>
@@ -37692,7 +37680,7 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="1" t="inlineStr">
+      <c r="A340" t="inlineStr">
         <is>
           <t>2017-08</t>
         </is>
@@ -37825,7 +37813,7 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" s="1" t="inlineStr">
+      <c r="A341" t="inlineStr">
         <is>
           <t>2017-09</t>
         </is>
@@ -37958,7 +37946,7 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" s="1" t="inlineStr">
+      <c r="A342" t="inlineStr">
         <is>
           <t>2017-10</t>
         </is>
@@ -38077,7 +38065,7 @@
       <c r="AQ342" t="inlineStr"/>
     </row>
     <row r="343">
-      <c r="A343" s="1" t="inlineStr">
+      <c r="A343" t="inlineStr">
         <is>
           <t>2017-11</t>
         </is>
@@ -38210,7 +38198,7 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="1" t="inlineStr">
+      <c r="A344" t="inlineStr">
         <is>
           <t>2017-12</t>
         </is>
@@ -38343,7 +38331,7 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" s="1" t="inlineStr">
+      <c r="A345" t="inlineStr">
         <is>
           <t>2018-01</t>
         </is>
@@ -38476,7 +38464,7 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="1" t="inlineStr">
+      <c r="A346" t="inlineStr">
         <is>
           <t>2018-02</t>
         </is>
@@ -38609,7 +38597,7 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" s="1" t="inlineStr">
+      <c r="A347" t="inlineStr">
         <is>
           <t>2018-03</t>
         </is>
@@ -38742,7 +38730,7 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" s="1" t="inlineStr">
+      <c r="A348" t="inlineStr">
         <is>
           <t>2018-04</t>
         </is>
@@ -38875,7 +38863,7 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" s="1" t="inlineStr">
+      <c r="A349" t="inlineStr">
         <is>
           <t>2018-05</t>
         </is>
@@ -39008,7 +38996,7 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="1" t="inlineStr">
+      <c r="A350" t="inlineStr">
         <is>
           <t>2018-06</t>
         </is>
@@ -39141,7 +39129,7 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" s="1" t="inlineStr">
+      <c r="A351" t="inlineStr">
         <is>
           <t>2018-07</t>
         </is>
@@ -39274,7 +39262,7 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="1" t="inlineStr">
+      <c r="A352" t="inlineStr">
         <is>
           <t>2018-08</t>
         </is>
@@ -39407,7 +39395,7 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="1" t="inlineStr">
+      <c r="A353" t="inlineStr">
         <is>
           <t>2018-09</t>
         </is>
@@ -39538,7 +39526,7 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" s="1" t="inlineStr">
+      <c r="A354" t="inlineStr">
         <is>
           <t>2018-10</t>
         </is>
@@ -39671,7 +39659,7 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" s="1" t="inlineStr">
+      <c r="A355" t="inlineStr">
         <is>
           <t>2018-11</t>
         </is>
@@ -39804,7 +39792,7 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" s="1" t="inlineStr">
+      <c r="A356" t="inlineStr">
         <is>
           <t>2018-12</t>
         </is>
@@ -39937,7 +39925,7 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" s="1" t="inlineStr">
+      <c r="A357" t="inlineStr">
         <is>
           <t>2019-01</t>
         </is>
@@ -40070,7 +40058,7 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" s="1" t="inlineStr">
+      <c r="A358" t="inlineStr">
         <is>
           <t>2019-02</t>
         </is>
@@ -40203,7 +40191,7 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="1" t="inlineStr">
+      <c r="A359" t="inlineStr">
         <is>
           <t>2019-03</t>
         </is>
@@ -40336,7 +40324,7 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="1" t="inlineStr">
+      <c r="A360" t="inlineStr">
         <is>
           <t>2019-04</t>
         </is>
@@ -40469,7 +40457,7 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" s="1" t="inlineStr">
+      <c r="A361" t="inlineStr">
         <is>
           <t>2019-05</t>
         </is>
@@ -40602,7 +40590,7 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" s="1" t="inlineStr">
+      <c r="A362" t="inlineStr">
         <is>
           <t>2019-06</t>
         </is>
@@ -40735,7 +40723,7 @@
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="1" t="inlineStr">
+      <c r="A363" t="inlineStr">
         <is>
           <t>2019-07</t>
         </is>
@@ -40868,7 +40856,7 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="1" t="inlineStr">
+      <c r="A364" t="inlineStr">
         <is>
           <t>2019-08</t>
         </is>
@@ -41001,7 +40989,7 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" s="1" t="inlineStr">
+      <c r="A365" t="inlineStr">
         <is>
           <t>2019-09</t>
         </is>
@@ -41134,7 +41122,7 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" s="1" t="inlineStr">
+      <c r="A366" t="inlineStr">
         <is>
           <t>2019-10</t>
         </is>
@@ -41267,7 +41255,7 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" s="1" t="inlineStr">
+      <c r="A367" t="inlineStr">
         <is>
           <t>2019-11</t>
         </is>
@@ -41400,7 +41388,7 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="1" t="inlineStr">
+      <c r="A368" t="inlineStr">
         <is>
           <t>2019-12</t>
         </is>
@@ -41533,7 +41521,7 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="1" t="inlineStr">
+      <c r="A369" t="inlineStr">
         <is>
           <t>2020-01</t>
         </is>
@@ -41666,7 +41654,7 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="1" t="inlineStr">
+      <c r="A370" t="inlineStr">
         <is>
           <t>2020-02</t>
         </is>
@@ -41799,7 +41787,7 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="1" t="inlineStr">
+      <c r="A371" t="inlineStr">
         <is>
           <t>2020-03</t>
         </is>
@@ -41932,7 +41920,7 @@
       </c>
     </row>
     <row r="372">
-      <c r="A372" s="1" t="inlineStr">
+      <c r="A372" t="inlineStr">
         <is>
           <t>2020-04</t>
         </is>
@@ -42065,7 +42053,7 @@
       </c>
     </row>
     <row r="373">
-      <c r="A373" s="1" t="inlineStr">
+      <c r="A373" t="inlineStr">
         <is>
           <t>2020-05</t>
         </is>
@@ -42198,7 +42186,7 @@
       </c>
     </row>
     <row r="374">
-      <c r="A374" s="1" t="inlineStr">
+      <c r="A374" t="inlineStr">
         <is>
           <t>2020-06</t>
         </is>
@@ -42331,7 +42319,7 @@
       </c>
     </row>
     <row r="375">
-      <c r="A375" s="1" t="inlineStr">
+      <c r="A375" t="inlineStr">
         <is>
           <t>2020-07</t>
         </is>
@@ -42464,7 +42452,7 @@
       </c>
     </row>
     <row r="376">
-      <c r="A376" s="1" t="inlineStr">
+      <c r="A376" t="inlineStr">
         <is>
           <t>2020-08</t>
         </is>
@@ -42597,7 +42585,7 @@
       </c>
     </row>
     <row r="377">
-      <c r="A377" s="1" t="inlineStr">
+      <c r="A377" t="inlineStr">
         <is>
           <t>2020-09</t>
         </is>
@@ -42730,7 +42718,7 @@
       </c>
     </row>
     <row r="378">
-      <c r="A378" s="1" t="inlineStr">
+      <c r="A378" t="inlineStr">
         <is>
           <t>2020-10</t>
         </is>
@@ -42863,7 +42851,7 @@
       </c>
     </row>
     <row r="379">
-      <c r="A379" s="1" t="inlineStr">
+      <c r="A379" t="inlineStr">
         <is>
           <t>2020-11</t>
         </is>
@@ -42996,7 +42984,7 @@
       </c>
     </row>
     <row r="380">
-      <c r="A380" s="1" t="inlineStr">
+      <c r="A380" t="inlineStr">
         <is>
           <t>2020-12</t>
         </is>
@@ -43129,7 +43117,7 @@
       </c>
     </row>
     <row r="381">
-      <c r="A381" s="1" t="inlineStr">
+      <c r="A381" t="inlineStr">
         <is>
           <t>2021-01</t>
         </is>
@@ -43262,7 +43250,7 @@
       </c>
     </row>
     <row r="382">
-      <c r="A382" s="1" t="inlineStr">
+      <c r="A382" t="inlineStr">
         <is>
           <t>2021-02</t>
         </is>
@@ -43395,7 +43383,7 @@
       </c>
     </row>
     <row r="383">
-      <c r="A383" s="1" t="inlineStr">
+      <c r="A383" t="inlineStr">
         <is>
           <t>2021-03</t>
         </is>
@@ -43528,7 +43516,7 @@
       </c>
     </row>
     <row r="384">
-      <c r="A384" s="1" t="inlineStr">
+      <c r="A384" t="inlineStr">
         <is>
           <t>2021-04</t>
         </is>
@@ -43661,7 +43649,7 @@
       </c>
     </row>
     <row r="385">
-      <c r="A385" s="1" t="inlineStr">
+      <c r="A385" t="inlineStr">
         <is>
           <t>2021-05</t>
         </is>
@@ -43794,7 +43782,7 @@
       </c>
     </row>
     <row r="386">
-      <c r="A386" s="1" t="inlineStr">
+      <c r="A386" t="inlineStr">
         <is>
           <t>2021-06</t>
         </is>
@@ -43927,7 +43915,7 @@
       </c>
     </row>
     <row r="387">
-      <c r="A387" s="1" t="inlineStr">
+      <c r="A387" t="inlineStr">
         <is>
           <t>2021-07</t>
         </is>
@@ -44060,7 +44048,7 @@
       </c>
     </row>
     <row r="388">
-      <c r="A388" s="1" t="inlineStr">
+      <c r="A388" t="inlineStr">
         <is>
           <t>2021-08</t>
         </is>
@@ -44193,7 +44181,7 @@
       </c>
     </row>
     <row r="389">
-      <c r="A389" s="1" t="inlineStr">
+      <c r="A389" t="inlineStr">
         <is>
           <t>2021-09</t>
         </is>
@@ -44326,7 +44314,7 @@
       </c>
     </row>
     <row r="390">
-      <c r="A390" s="1" t="inlineStr">
+      <c r="A390" t="inlineStr">
         <is>
           <t>2021-10</t>
         </is>
@@ -44445,7 +44433,7 @@
       </c>
     </row>
     <row r="391">
-      <c r="A391" s="1" t="inlineStr">
+      <c r="A391" t="inlineStr">
         <is>
           <t>2021-11</t>
         </is>
@@ -44578,7 +44566,7 @@
       </c>
     </row>
     <row r="392">
-      <c r="A392" s="1" t="inlineStr">
+      <c r="A392" t="inlineStr">
         <is>
           <t>2021-12</t>
         </is>
@@ -44711,7 +44699,7 @@
       </c>
     </row>
     <row r="393">
-      <c r="A393" s="1" t="inlineStr">
+      <c r="A393" t="inlineStr">
         <is>
           <t>2022-01</t>
         </is>
@@ -44844,7 +44832,7 @@
       </c>
     </row>
     <row r="394">
-      <c r="A394" s="1" t="inlineStr">
+      <c r="A394" t="inlineStr">
         <is>
           <t>2022-02</t>
         </is>
@@ -44977,7 +44965,7 @@
       </c>
     </row>
     <row r="395">
-      <c r="A395" s="1" t="inlineStr">
+      <c r="A395" t="inlineStr">
         <is>
           <t>2022-03</t>
         </is>
@@ -45110,7 +45098,7 @@
       </c>
     </row>
     <row r="396">
-      <c r="A396" s="1" t="inlineStr">
+      <c r="A396" t="inlineStr">
         <is>
           <t>2022-04</t>
         </is>
@@ -45243,7 +45231,7 @@
       </c>
     </row>
     <row r="397">
-      <c r="A397" s="1" t="inlineStr">
+      <c r="A397" t="inlineStr">
         <is>
           <t>2022-05</t>
         </is>
@@ -45376,7 +45364,7 @@
       </c>
     </row>
     <row r="398">
-      <c r="A398" s="1" t="inlineStr">
+      <c r="A398" t="inlineStr">
         <is>
           <t>2022-06</t>
         </is>
@@ -45509,7 +45497,7 @@
       </c>
     </row>
     <row r="399">
-      <c r="A399" s="1" t="inlineStr">
+      <c r="A399" t="inlineStr">
         <is>
           <t>2022-07</t>
         </is>
@@ -45642,7 +45630,7 @@
       </c>
     </row>
     <row r="400">
-      <c r="A400" s="1" t="inlineStr">
+      <c r="A400" t="inlineStr">
         <is>
           <t>2022-08</t>
         </is>
@@ -45775,7 +45763,7 @@
       </c>
     </row>
     <row r="401">
-      <c r="A401" s="1" t="inlineStr">
+      <c r="A401" t="inlineStr">
         <is>
           <t>2022-09</t>
         </is>
@@ -45908,7 +45896,7 @@
       </c>
     </row>
     <row r="402">
-      <c r="A402" s="1" t="inlineStr">
+      <c r="A402" t="inlineStr">
         <is>
           <t>2022-10</t>
         </is>
@@ -46041,7 +46029,7 @@
       </c>
     </row>
     <row r="403">
-      <c r="A403" s="1" t="inlineStr">
+      <c r="A403" t="inlineStr">
         <is>
           <t>2022-11</t>
         </is>
@@ -46174,7 +46162,7 @@
       </c>
     </row>
     <row r="404">
-      <c r="A404" s="1" t="inlineStr">
+      <c r="A404" t="inlineStr">
         <is>
           <t>2022-12</t>
         </is>
@@ -46307,7 +46295,7 @@
       </c>
     </row>
     <row r="405">
-      <c r="A405" s="1" t="inlineStr">
+      <c r="A405" t="inlineStr">
         <is>
           <t>2023-01</t>
         </is>
@@ -46440,7 +46428,7 @@
       </c>
     </row>
     <row r="406">
-      <c r="A406" s="1" t="inlineStr">
+      <c r="A406" t="inlineStr">
         <is>
           <t>2023-02</t>
         </is>
@@ -46573,7 +46561,7 @@
       </c>
     </row>
     <row r="407">
-      <c r="A407" s="1" t="inlineStr">
+      <c r="A407" t="inlineStr">
         <is>
           <t>2023-03</t>
         </is>
@@ -46706,7 +46694,7 @@
       </c>
     </row>
     <row r="408">
-      <c r="A408" s="1" t="inlineStr">
+      <c r="A408" t="inlineStr">
         <is>
           <t>2023-04</t>
         </is>
@@ -46839,7 +46827,7 @@
       </c>
     </row>
     <row r="409">
-      <c r="A409" s="1" t="inlineStr">
+      <c r="A409" t="inlineStr">
         <is>
           <t>2023-05</t>
         </is>
@@ -46972,7 +46960,7 @@
       </c>
     </row>
     <row r="410">
-      <c r="A410" s="1" t="inlineStr">
+      <c r="A410" t="inlineStr">
         <is>
           <t>2023-06</t>
         </is>
@@ -47105,7 +47093,7 @@
       </c>
     </row>
     <row r="411">
-      <c r="A411" s="1" t="inlineStr">
+      <c r="A411" t="inlineStr">
         <is>
           <t>2023-07</t>
         </is>
@@ -47238,7 +47226,7 @@
       </c>
     </row>
     <row r="412">
-      <c r="A412" s="1" t="inlineStr">
+      <c r="A412" t="inlineStr">
         <is>
           <t>2023-08</t>
         </is>
@@ -47371,7 +47359,7 @@
       </c>
     </row>
     <row r="413">
-      <c r="A413" s="1" t="inlineStr">
+      <c r="A413" t="inlineStr">
         <is>
           <t>2023-09</t>
         </is>
@@ -47504,7 +47492,7 @@
       </c>
     </row>
     <row r="414">
-      <c r="A414" s="1" t="inlineStr">
+      <c r="A414" t="inlineStr">
         <is>
           <t>2023-10</t>
         </is>
@@ -47637,7 +47625,7 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" s="1" t="inlineStr">
+      <c r="A415" t="inlineStr">
         <is>
           <t>2023-11</t>
         </is>
@@ -47770,7 +47758,7 @@
       </c>
     </row>
     <row r="416">
-      <c r="A416" s="1" t="inlineStr">
+      <c r="A416" t="inlineStr">
         <is>
           <t>2023-12</t>
         </is>
@@ -47903,7 +47891,7 @@
       </c>
     </row>
     <row r="417">
-      <c r="A417" s="1" t="inlineStr">
+      <c r="A417" t="inlineStr">
         <is>
           <t>2024-01</t>
         </is>
@@ -48026,7 +48014,7 @@
       </c>
     </row>
     <row r="418">
-      <c r="A418" s="1" t="inlineStr">
+      <c r="A418" t="inlineStr">
         <is>
           <t>2024-02</t>
         </is>
@@ -48159,7 +48147,7 @@
       </c>
     </row>
     <row r="419">
-      <c r="A419" s="1" t="inlineStr">
+      <c r="A419" t="inlineStr">
         <is>
           <t>2024-03</t>
         </is>
@@ -48292,7 +48280,7 @@
       </c>
     </row>
     <row r="420">
-      <c r="A420" s="1" t="inlineStr">
+      <c r="A420" t="inlineStr">
         <is>
           <t>2024-04</t>
         </is>
@@ -48425,7 +48413,7 @@
       </c>
     </row>
     <row r="421">
-      <c r="A421" s="1" t="inlineStr">
+      <c r="A421" t="inlineStr">
         <is>
           <t>2024-05</t>
         </is>
@@ -48558,7 +48546,7 @@
       </c>
     </row>
     <row r="422">
-      <c r="A422" s="1" t="inlineStr">
+      <c r="A422" t="inlineStr">
         <is>
           <t>2024-06</t>
         </is>
@@ -48691,7 +48679,7 @@
       </c>
     </row>
     <row r="423">
-      <c r="A423" s="1" t="inlineStr">
+      <c r="A423" t="inlineStr">
         <is>
           <t>2024-07</t>
         </is>
@@ -48824,7 +48812,7 @@
       </c>
     </row>
     <row r="424">
-      <c r="A424" s="1" t="inlineStr">
+      <c r="A424" t="inlineStr">
         <is>
           <t>2024-08</t>
         </is>
@@ -48957,7 +48945,7 @@
       </c>
     </row>
     <row r="425">
-      <c r="A425" s="1" t="inlineStr">
+      <c r="A425" t="inlineStr">
         <is>
           <t>2024-09</t>
         </is>
@@ -49090,7 +49078,7 @@
       </c>
     </row>
     <row r="426">
-      <c r="A426" s="1" t="inlineStr">
+      <c r="A426" t="inlineStr">
         <is>
           <t>2024-10</t>
         </is>
@@ -49223,7 +49211,7 @@
       </c>
     </row>
     <row r="427">
-      <c r="A427" s="1" t="inlineStr">
+      <c r="A427" t="inlineStr">
         <is>
           <t>2024-11</t>
         </is>
@@ -49356,7 +49344,7 @@
       </c>
     </row>
     <row r="428">
-      <c r="A428" s="1" t="inlineStr">
+      <c r="A428" t="inlineStr">
         <is>
           <t>2024-12</t>
         </is>
@@ -49489,7 +49477,7 @@
       </c>
     </row>
     <row r="429">
-      <c r="A429" s="1" t="inlineStr">
+      <c r="A429" t="inlineStr">
         <is>
           <t>2025-01</t>
         </is>
@@ -49622,7 +49610,7 @@
       </c>
     </row>
     <row r="430">
-      <c r="A430" s="1" t="inlineStr">
+      <c r="A430" t="inlineStr">
         <is>
           <t>2025-02</t>
         </is>
@@ -49755,7 +49743,7 @@
       </c>
     </row>
     <row r="431">
-      <c r="A431" s="1" t="inlineStr">
+      <c r="A431" t="inlineStr">
         <is>
           <t>2025-03</t>
         </is>
@@ -49888,7 +49876,7 @@
       </c>
     </row>
     <row r="432">
-      <c r="A432" s="1" t="inlineStr">
+      <c r="A432" t="inlineStr">
         <is>
           <t>2025-04</t>
         </is>
@@ -50021,7 +50009,7 @@
       </c>
     </row>
     <row r="433">
-      <c r="A433" s="1" t="inlineStr">
+      <c r="A433" t="inlineStr">
         <is>
           <t>2025-05</t>
         </is>
@@ -50154,7 +50142,7 @@
       </c>
     </row>
     <row r="434">
-      <c r="A434" s="1" t="inlineStr">
+      <c r="A434" t="inlineStr">
         <is>
           <t>2025-06</t>
         </is>
@@ -50287,7 +50275,7 @@
       </c>
     </row>
     <row r="435">
-      <c r="A435" s="1" t="inlineStr">
+      <c r="A435" t="inlineStr">
         <is>
           <t>2025-07</t>
         </is>
@@ -50420,7 +50408,7 @@
       </c>
     </row>
     <row r="436">
-      <c r="A436" s="1" t="inlineStr">
+      <c r="A436" t="inlineStr">
         <is>
           <t>2025-08</t>
         </is>
@@ -50553,7 +50541,7 @@
       </c>
     </row>
     <row r="437">
-      <c r="A437" s="1" t="inlineStr">
+      <c r="A437" t="inlineStr">
         <is>
           <t>2025-09</t>
         </is>
@@ -50686,7 +50674,7 @@
       </c>
     </row>
     <row r="438">
-      <c r="A438" s="1" t="inlineStr">
+      <c r="A438" t="inlineStr">
         <is>
           <t>2025-10</t>
         </is>
@@ -50819,7 +50807,7 @@
       </c>
     </row>
     <row r="439">
-      <c r="A439" s="1" t="inlineStr">
+      <c r="A439" t="inlineStr">
         <is>
           <t>2025-11</t>
         </is>
@@ -50952,7 +50940,7 @@
       </c>
     </row>
     <row r="440">
-      <c r="A440" s="1" t="inlineStr">
+      <c r="A440" t="inlineStr">
         <is>
           <t>2025-12</t>
         </is>
@@ -51085,7 +51073,7 @@
       </c>
     </row>
     <row r="441">
-      <c r="A441" s="1" t="inlineStr">
+      <c r="A441" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
@@ -51218,7 +51206,7 @@
       </c>
     </row>
     <row r="442">
-      <c r="A442" s="1" t="inlineStr">
+      <c r="A442" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
@@ -51351,7 +51339,7 @@
       </c>
     </row>
     <row r="443">
-      <c r="A443" s="1" t="inlineStr">
+      <c r="A443" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
@@ -51484,7 +51472,7 @@
       </c>
     </row>
     <row r="444">
-      <c r="A444" s="1" t="inlineStr">
+      <c r="A444" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
@@ -51493,13 +51481,13 @@
         <v>9.090909090909092</v>
       </c>
       <c r="C444" t="n">
-        <v>5.88235294117647</v>
+        <v>5.555555555555555</v>
       </c>
       <c r="D444" t="n">
         <v>58.33333333333334</v>
       </c>
       <c r="E444" t="n">
-        <v>58.82352941176471</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="F444" t="n">
         <v>9.090909090909092</v>
@@ -51511,31 +51499,31 @@
         <v>-1.544444444444445</v>
       </c>
       <c r="I444" t="n">
-        <v>-1.291176470588235</v>
+        <v>-0.5694444444444444</v>
       </c>
       <c r="J444" t="n">
         <v>-1.3</v>
       </c>
       <c r="K444" t="n">
-        <v>0.1176470588235294</v>
+        <v>0.8777777777777779</v>
       </c>
       <c r="L444" t="n">
         <v>0.09999999999999983</v>
       </c>
       <c r="M444" t="n">
-        <v>1.647058823529412</v>
+        <v>2.472222222222222</v>
       </c>
       <c r="N444" t="n">
         <v>4.454545454545455</v>
       </c>
       <c r="O444" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="P444" t="n">
         <v>46.09999999999999</v>
       </c>
       <c r="Q444" t="n">
-        <v>25.67647058823529</v>
+        <v>24.92222222222222</v>
       </c>
       <c r="R444" t="n">
         <v>-2</v>
@@ -51556,49 +51544,49 @@
         <v>58.33333333333334</v>
       </c>
       <c r="X444" t="n">
-        <v>41.17647058823529</v>
+        <v>38.88888888888889</v>
       </c>
       <c r="Y444" t="n">
         <v>25</v>
       </c>
       <c r="Z444" t="n">
-        <v>41.17647058823529</v>
+        <v>38.88888888888889</v>
       </c>
       <c r="AA444" t="n">
         <v>50</v>
       </c>
       <c r="AB444" t="n">
-        <v>58.82352941176471</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="AC444" t="n">
         <v>75</v>
       </c>
       <c r="AD444" t="n">
-        <v>81.25</v>
+        <v>76.47058823529412</v>
       </c>
       <c r="AE444" t="n">
         <v>11.33333333333334</v>
       </c>
       <c r="AF444" t="n">
-        <v>16</v>
+        <v>15.33333333333334</v>
       </c>
       <c r="AG444" t="n">
         <v>66.66666666666666</v>
       </c>
       <c r="AH444" t="n">
-        <v>52.94117647058824</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="AI444" t="n">
         <v>75</v>
       </c>
       <c r="AJ444" t="n">
-        <v>76.47058823529412</v>
+        <v>72.22222222222221</v>
       </c>
       <c r="AK444" t="n">
         <v>66.66666666666666</v>
       </c>
       <c r="AL444" t="n">
-        <v>29.41176470588236</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="AM444" t="n">
         <v>3.100000000000001</v>
@@ -51617,7 +51605,7 @@
       </c>
     </row>
     <row r="445">
-      <c r="A445" s="1" t="inlineStr">
+      <c r="A445" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
@@ -51750,7 +51738,7 @@
       </c>
     </row>
     <row r="446">
-      <c r="A446" s="1" t="inlineStr">
+      <c r="A446" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -51878,6 +51866,139 @@
       </c>
       <c r="AQ446" t="n">
         <v>5.166666666666667</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B447" t="n">
+        <v>0</v>
+      </c>
+      <c r="C447" t="n">
+        <v>0</v>
+      </c>
+      <c r="D447" t="n">
+        <v>45.45454545454545</v>
+      </c>
+      <c r="E447" t="n">
+        <v>36.36363636363637</v>
+      </c>
+      <c r="F447" t="n">
+        <v>10</v>
+      </c>
+      <c r="G447" t="n">
+        <v>49636.11111111111</v>
+      </c>
+      <c r="H447" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I447" t="n">
+        <v>3.469446951953614e-17</v>
+      </c>
+      <c r="J447" t="n">
+        <v>-0.1428571428571428</v>
+      </c>
+      <c r="K447" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L447" t="n">
+        <v>-0.5555555555555554</v>
+      </c>
+      <c r="M447" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="N447" t="n">
+        <v>4.666666666666666</v>
+      </c>
+      <c r="O447" t="n">
+        <v>2</v>
+      </c>
+      <c r="P447" t="n">
+        <v>64.25</v>
+      </c>
+      <c r="Q447" t="n">
+        <v>19.09090909090909</v>
+      </c>
+      <c r="R447" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S447" t="n">
+        <v>-1.45</v>
+      </c>
+      <c r="T447" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U447" t="n">
+        <v>4</v>
+      </c>
+      <c r="V447" t="n">
+        <v>38.75</v>
+      </c>
+      <c r="W447" t="n">
+        <v>70</v>
+      </c>
+      <c r="X447" t="n">
+        <v>36.36363636363637</v>
+      </c>
+      <c r="Y447" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z447" t="n">
+        <v>45.45454545454545</v>
+      </c>
+      <c r="AA447" t="n">
+        <v>63.63636363636363</v>
+      </c>
+      <c r="AB447" t="n">
+        <v>54.54545454545454</v>
+      </c>
+      <c r="AC447" t="n">
+        <v>45.45454545454545</v>
+      </c>
+      <c r="AD447" t="n">
+        <v>45.45454545454545</v>
+      </c>
+      <c r="AE447" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="AF447" t="n">
+        <v>24.36363636363637</v>
+      </c>
+      <c r="AG447" t="n">
+        <v>45.45454545454545</v>
+      </c>
+      <c r="AH447" t="n">
+        <v>45.45454545454545</v>
+      </c>
+      <c r="AI447" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ447" t="n">
+        <v>81.81818181818183</v>
+      </c>
+      <c r="AK447" t="n">
+        <v>36.36363636363637</v>
+      </c>
+      <c r="AL447" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM447" t="n">
+        <v>2.966363636363637</v>
+      </c>
+      <c r="AN447" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="AO447" t="n">
+        <v>3.167328571428571</v>
+      </c>
+      <c r="AP447" t="n">
+        <v>3.645</v>
+      </c>
+      <c r="AQ447" t="n">
+        <v>2.202142857142857</v>
       </c>
     </row>
   </sheetData>

--- a/static/data/Extended-Indexes.xlsx
+++ b/static/data/Extended-Indexes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ447"/>
+  <dimension ref="A1:AQ448"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52001,6 +52001,139 @@
         <v>2.202142857142857</v>
       </c>
     </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B448" t="n">
+        <v>0</v>
+      </c>
+      <c r="C448" t="n">
+        <v>0</v>
+      </c>
+      <c r="D448" t="n">
+        <v>30</v>
+      </c>
+      <c r="E448" t="n">
+        <v>55.55555555555556</v>
+      </c>
+      <c r="F448" t="n">
+        <v>0</v>
+      </c>
+      <c r="G448" t="n">
+        <v>51833.33333333334</v>
+      </c>
+      <c r="H448" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="I448" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="J448" t="n">
+        <v>3</v>
+      </c>
+      <c r="K448" t="n">
+        <v>0.4375000000000001</v>
+      </c>
+      <c r="L448" t="n">
+        <v>3.571428571428571</v>
+      </c>
+      <c r="M448" t="n">
+        <v>-1.6875</v>
+      </c>
+      <c r="N448" t="n">
+        <v>3.714285714285714</v>
+      </c>
+      <c r="O448" t="n">
+        <v>1.444444444444445</v>
+      </c>
+      <c r="P448" t="n">
+        <v>71.125</v>
+      </c>
+      <c r="Q448" t="n">
+        <v>32.31250000000001</v>
+      </c>
+      <c r="R448" t="n">
+        <v>0.9999999999999999</v>
+      </c>
+      <c r="S448" t="n">
+        <v>5.666666666666667</v>
+      </c>
+      <c r="T448" t="n">
+        <v>4</v>
+      </c>
+      <c r="U448" t="n">
+        <v>4</v>
+      </c>
+      <c r="V448" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W448" t="n">
+        <v>50</v>
+      </c>
+      <c r="X448" t="n">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="Y448" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z448" t="n">
+        <v>27.77777777777778</v>
+      </c>
+      <c r="AA448" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB448" t="n">
+        <v>61.11111111111111</v>
+      </c>
+      <c r="AC448" t="n">
+        <v>60</v>
+      </c>
+      <c r="AD448" t="n">
+        <v>38.88888888888889</v>
+      </c>
+      <c r="AE448" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="AF448" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="AG448" t="n">
+        <v>80</v>
+      </c>
+      <c r="AH448" t="n">
+        <v>77.77777777777779</v>
+      </c>
+      <c r="AI448" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ448" t="n">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="AK448" t="n">
+        <v>77.77777777777779</v>
+      </c>
+      <c r="AL448" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="AM448" t="n">
+        <v>3.509999999999999</v>
+      </c>
+      <c r="AN448" t="n">
+        <v>4.357142857142858</v>
+      </c>
+      <c r="AO448" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="AP448" t="n">
+        <v>4.5625</v>
+      </c>
+      <c r="AQ448" t="n">
+        <v>2.875</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
